--- a/razvoj softverskih projekata.xlsx
+++ b/razvoj softverskih projekata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Tamara Rancic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5BA8343-0FFA-4444-BA6E-42A728BA4F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7C7EB3-76C3-4C96-AE5D-66C97EA8530F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AD1EEFCA-D0A5-4B47-846B-7060607D7D4B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
   <si>
     <t xml:space="preserve"> BACKLOG  </t>
   </si>
@@ -516,7 +516,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
-    <col min="2" max="2" width="27.5703125" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" customWidth="1"/>
     <col min="3" max="3" width="33.140625" customWidth="1"/>
     <col min="4" max="4" width="25.85546875" customWidth="1"/>
     <col min="5" max="5" width="26.85546875" customWidth="1"/>
@@ -546,6 +546,9 @@
       <c r="B2" t="s">
         <v>9</v>
       </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="3" spans="1:5" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -554,6 +557,9 @@
       <c r="B3" t="s">
         <v>10</v>
       </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="4" spans="1:5" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
@@ -562,12 +568,18 @@
       <c r="B4" s="7" t="s">
         <v>11</v>
       </c>
+      <c r="C4" s="7" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="5" spans="1:5" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
         <v>12</v>
       </c>
     </row>
